--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_14-07-2025.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-tb4025-2400x1200x25mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-tb4030-2400x1200x30mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-tb4040-2400x1200x40mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4050-2400x1200x50mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4060-2400x1200x60mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4070-2400x1200x70mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4075-2400x1200x75mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4080-2400x1200x80mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4090-2400x1200x90mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-ga4100-2400x1200x100mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-xr4110-insulation-2400x1200x110mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-xr4120-2400x1200x120mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-xr4130-2400x1200x130mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-xr4140-2400x1200x140mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-xr4150-2400x1200x150mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-pl4025-ins-plasterboard-25mm-12-5mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-pl4050-ins-plasterboard-50mm-12-5mm</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-cavity-insulation-cw4050-450mm-x-1200mm-pack-of-11</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4075-450mm-x-1200mm-pack-of-8</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.directinsulation.com/product-page/celotex-cavity-cw4100-450mm-x-1200mm-pack-of-6</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
